--- a/data/nzd0401/nzd0401.xlsx
+++ b/data/nzd0401/nzd0401.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L403"/>
+  <dimension ref="A1:L405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17372,6 +17372,90 @@
         <v>322.47</v>
       </c>
       <c r="L403" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>328</v>
+      </c>
+      <c r="C404" t="n">
+        <v>331.62</v>
+      </c>
+      <c r="D404" t="n">
+        <v>337.24</v>
+      </c>
+      <c r="E404" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="F404" t="n">
+        <v>323.49</v>
+      </c>
+      <c r="G404" t="n">
+        <v>314.74</v>
+      </c>
+      <c r="H404" t="n">
+        <v>318.81</v>
+      </c>
+      <c r="I404" t="n">
+        <v>321.03</v>
+      </c>
+      <c r="J404" t="n">
+        <v>323.05</v>
+      </c>
+      <c r="K404" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>327.49</v>
+      </c>
+      <c r="C405" t="n">
+        <v>331.49</v>
+      </c>
+      <c r="D405" t="n">
+        <v>337</v>
+      </c>
+      <c r="E405" t="n">
+        <v>326.78</v>
+      </c>
+      <c r="F405" t="n">
+        <v>322.57</v>
+      </c>
+      <c r="G405" t="n">
+        <v>314.45</v>
+      </c>
+      <c r="H405" t="n">
+        <v>318.22</v>
+      </c>
+      <c r="I405" t="n">
+        <v>321.34</v>
+      </c>
+      <c r="J405" t="n">
+        <v>323.28</v>
+      </c>
+      <c r="K405" t="n">
+        <v>323.02</v>
+      </c>
+      <c r="L405" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17388,7 +17472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B406"/>
+  <dimension ref="A1:B408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21451,6 +21535,26 @@
       </c>
       <c r="B406" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21619,28 +21723,28 @@
         <v>0.1636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7625944802278545</v>
+        <v>0.7549857836451052</v>
       </c>
       <c r="J2" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K2" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5390514531506083</v>
+        <v>0.5340289048296611</v>
       </c>
       <c r="M2" t="n">
-        <v>4.400280352738379</v>
+        <v>4.412970323915848</v>
       </c>
       <c r="N2" t="n">
-        <v>27.75184451739481</v>
+        <v>27.91617923596315</v>
       </c>
       <c r="O2" t="n">
-        <v>5.268001947360575</v>
+        <v>5.283576367950324</v>
       </c>
       <c r="P2" t="n">
-        <v>315.1126535800467</v>
+        <v>315.1947413036046</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21697,28 +21801,28 @@
         <v>0.1733</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7467738142169779</v>
+        <v>0.7415838284323226</v>
       </c>
       <c r="J3" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K3" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4819782624026103</v>
+        <v>0.4801234692283612</v>
       </c>
       <c r="M3" t="n">
-        <v>4.677264595497669</v>
+        <v>4.675525331925823</v>
       </c>
       <c r="N3" t="n">
-        <v>33.44883561325486</v>
+        <v>33.42350530240549</v>
       </c>
       <c r="O3" t="n">
-        <v>5.783496832648468</v>
+        <v>5.78130653939103</v>
       </c>
       <c r="P3" t="n">
-        <v>316.8503076993659</v>
+        <v>316.9062997443897</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21775,28 +21879,28 @@
         <v>0.1687</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4664792818184871</v>
+        <v>0.462126877226209</v>
       </c>
       <c r="J4" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K4" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3719340792207591</v>
+        <v>0.3689373318244544</v>
       </c>
       <c r="M4" t="n">
-        <v>3.552328624807051</v>
+        <v>3.557531851282617</v>
       </c>
       <c r="N4" t="n">
-        <v>20.50625175569139</v>
+        <v>20.50343184877972</v>
       </c>
       <c r="O4" t="n">
-        <v>4.528382907362339</v>
+        <v>4.528071537506858</v>
       </c>
       <c r="P4" t="n">
-        <v>329.0818154033518</v>
+        <v>329.1287718262288</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21853,28 +21957,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0998283415003499</v>
+        <v>0.09597172287889798</v>
       </c>
       <c r="J5" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K5" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06957178550478094</v>
+        <v>0.06465745933191869</v>
       </c>
       <c r="M5" t="n">
-        <v>2.210233563465528</v>
+        <v>2.223140907985559</v>
       </c>
       <c r="N5" t="n">
-        <v>7.43771861334915</v>
+        <v>7.478643841992187</v>
       </c>
       <c r="O5" t="n">
-        <v>2.727218108870127</v>
+        <v>2.734710924758262</v>
       </c>
       <c r="P5" t="n">
-        <v>328.342556339399</v>
+        <v>328.3841653237296</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21935,28 +22039,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1499419539335279</v>
+        <v>-0.1514909152116334</v>
       </c>
       <c r="J6" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K6" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09979597337105972</v>
+        <v>0.1025308748972357</v>
       </c>
       <c r="M6" t="n">
-        <v>2.475583982326831</v>
+        <v>2.473033728632265</v>
       </c>
       <c r="N6" t="n">
-        <v>11.31765821278653</v>
+        <v>11.27514794282886</v>
       </c>
       <c r="O6" t="n">
-        <v>3.364172738250301</v>
+        <v>3.357848707555012</v>
       </c>
       <c r="P6" t="n">
-        <v>328.6597810964872</v>
+        <v>328.6764963137477</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22017,28 +22121,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1516512354052605</v>
+        <v>0.1489209207844031</v>
       </c>
       <c r="J7" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K7" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08007299828032965</v>
+        <v>0.07801584850770216</v>
       </c>
       <c r="M7" t="n">
-        <v>2.909068210601955</v>
+        <v>2.90947447524171</v>
       </c>
       <c r="N7" t="n">
-        <v>14.74488842637927</v>
+        <v>14.71079901131587</v>
       </c>
       <c r="O7" t="n">
-        <v>3.839907346066995</v>
+        <v>3.835465944486519</v>
       </c>
       <c r="P7" t="n">
-        <v>313.3414180128571</v>
+        <v>313.3708749400881</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22095,28 +22199,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02870220429198197</v>
+        <v>0.02317790589374367</v>
       </c>
       <c r="J8" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K8" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004024769207435108</v>
+        <v>0.002619752411353371</v>
       </c>
       <c r="M8" t="n">
-        <v>2.636221178768903</v>
+        <v>2.654610302722112</v>
       </c>
       <c r="N8" t="n">
-        <v>11.37680642085163</v>
+        <v>11.47976827018505</v>
       </c>
       <c r="O8" t="n">
-        <v>3.372952181821088</v>
+        <v>3.388180672600718</v>
       </c>
       <c r="P8" t="n">
-        <v>323.4523628209851</v>
+        <v>323.5119636348245</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22173,28 +22277,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02003100179442369</v>
+        <v>-0.02449539077650419</v>
       </c>
       <c r="J9" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K9" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002863144500882542</v>
+        <v>0.004264582620378765</v>
       </c>
       <c r="M9" t="n">
-        <v>2.201275414303397</v>
+        <v>2.209998277733615</v>
       </c>
       <c r="N9" t="n">
-        <v>7.798285859205328</v>
+        <v>7.863581337328823</v>
       </c>
       <c r="O9" t="n">
-        <v>2.792541111461983</v>
+        <v>2.804207791396498</v>
       </c>
       <c r="P9" t="n">
-        <v>326.3382057725172</v>
+        <v>326.3863674431867</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22251,28 +22355,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1107194601887071</v>
+        <v>0.1069603718150688</v>
       </c>
       <c r="J10" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K10" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09202031771781982</v>
+        <v>0.08639447884942553</v>
       </c>
       <c r="M10" t="n">
-        <v>2.102569873482731</v>
+        <v>2.110952998275613</v>
       </c>
       <c r="N10" t="n">
-        <v>6.750293111488615</v>
+        <v>6.790515594490346</v>
       </c>
       <c r="O10" t="n">
-        <v>2.598132620073236</v>
+        <v>2.605861775783656</v>
       </c>
       <c r="P10" t="n">
-        <v>324.0748481473791</v>
+        <v>324.1154012496945</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22329,28 +22433,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08262369826738002</v>
+        <v>-0.08739450530709111</v>
       </c>
       <c r="J11" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K11" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06483877409325178</v>
+        <v>0.07127370011339118</v>
       </c>
       <c r="M11" t="n">
-        <v>1.871442598356015</v>
+        <v>1.885837031121971</v>
       </c>
       <c r="N11" t="n">
-        <v>5.494690902981764</v>
+        <v>5.5861283791939</v>
       </c>
       <c r="O11" t="n">
-        <v>2.344075703338475</v>
+        <v>2.363499181128248</v>
       </c>
       <c r="P11" t="n">
-        <v>330.0074864835461</v>
+        <v>330.0589538616254</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22388,7 +22492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L403"/>
+  <dimension ref="A1:L405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47377,6 +47481,130 @@
         </is>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>-42.74882951553152,173.3937352605792</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>-42.74944081873214,173.3933950153586</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>-42.75006989924028,173.39307079161554</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>-42.75071052212487,173.3927876936825</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>-42.751327838895655,173.39255961704063</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>-42.75187006475329,173.3921463214296</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>-42.752464720188016,173.3917564317915</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>-42.75310551493852,173.39145509182003</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>-42.753724799844846,173.3911636265607</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>-42.75432591391904,173.39080938620123</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>-42.74882758564839,173.39372960581505</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>-42.74944032679854,173.39339357393558</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>-42.750069250366934,173.39306799431264</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>-42.750709624564884,173.3927814574856</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>-42.75132543436871,173.39254885910347</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>-42.75186895059063,173.3921431164589</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-42.752462511159806,173.39174987490037</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>-42.75310649081286,173.39145864094434</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>-42.75372556542062,173.39116623808414</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>-42.754327036377724,173.39081298775255</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0401/nzd0401.xlsx
+++ b/data/nzd0401/nzd0401.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L405"/>
+  <dimension ref="A1:L407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17456,6 +17456,90 @@
         <v>323.02</v>
       </c>
       <c r="L405" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>327.13</v>
+      </c>
+      <c r="C406" t="n">
+        <v>331.58</v>
+      </c>
+      <c r="D406" t="n">
+        <v>336.69</v>
+      </c>
+      <c r="E406" t="n">
+        <v>326.83</v>
+      </c>
+      <c r="F406" t="n">
+        <v>322.31</v>
+      </c>
+      <c r="G406" t="n">
+        <v>314.63</v>
+      </c>
+      <c r="H406" t="n">
+        <v>318.05</v>
+      </c>
+      <c r="I406" t="n">
+        <v>321.39</v>
+      </c>
+      <c r="J406" t="n">
+        <v>323.06</v>
+      </c>
+      <c r="K406" t="n">
+        <v>323.31</v>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>328.14</v>
+      </c>
+      <c r="C407" t="n">
+        <v>331.48</v>
+      </c>
+      <c r="D407" t="n">
+        <v>336.63</v>
+      </c>
+      <c r="E407" t="n">
+        <v>326.95</v>
+      </c>
+      <c r="F407" t="n">
+        <v>322.61</v>
+      </c>
+      <c r="G407" t="n">
+        <v>315.33</v>
+      </c>
+      <c r="H407" t="n">
+        <v>318.61</v>
+      </c>
+      <c r="I407" t="n">
+        <v>322.13</v>
+      </c>
+      <c r="J407" t="n">
+        <v>323.16</v>
+      </c>
+      <c r="K407" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="L407" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17472,7 +17556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B408"/>
+  <dimension ref="A1:B410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21555,6 +21639,26 @@
       </c>
       <c r="B408" t="n">
         <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -21723,28 +21827,28 @@
         <v>0.1636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7549857836451052</v>
+        <v>0.7474032211086346</v>
       </c>
       <c r="J2" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K2" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5340289048296611</v>
+        <v>0.528941476139415</v>
       </c>
       <c r="M2" t="n">
-        <v>4.412970323915848</v>
+        <v>4.426448838015467</v>
       </c>
       <c r="N2" t="n">
-        <v>27.91617923596315</v>
+        <v>28.0829706024877</v>
       </c>
       <c r="O2" t="n">
-        <v>5.283576367950324</v>
+        <v>5.299336807798472</v>
       </c>
       <c r="P2" t="n">
-        <v>315.1947413036046</v>
+        <v>315.2768065638746</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21801,28 +21905,28 @@
         <v>0.1733</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7415838284323226</v>
+        <v>0.7364389270698364</v>
       </c>
       <c r="J3" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K3" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4801234692283612</v>
+        <v>0.4782621518926565</v>
       </c>
       <c r="M3" t="n">
-        <v>4.675525331925823</v>
+        <v>4.673679261902903</v>
       </c>
       <c r="N3" t="n">
-        <v>33.42350530240549</v>
+        <v>33.39840088082136</v>
       </c>
       <c r="O3" t="n">
-        <v>5.78130653939103</v>
+        <v>5.779134959561107</v>
       </c>
       <c r="P3" t="n">
-        <v>316.9062997443897</v>
+        <v>316.9619883782142</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21879,28 +21983,28 @@
         <v>0.1687</v>
       </c>
       <c r="I4" t="n">
-        <v>0.462126877226209</v>
+        <v>0.4574042218304851</v>
       </c>
       <c r="J4" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K4" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3689373318244544</v>
+        <v>0.3653041132514294</v>
       </c>
       <c r="M4" t="n">
-        <v>3.557531851282617</v>
+        <v>3.564697109906596</v>
       </c>
       <c r="N4" t="n">
-        <v>20.50343184877972</v>
+        <v>20.51999875693141</v>
       </c>
       <c r="O4" t="n">
-        <v>4.528071537506858</v>
+        <v>4.5299005239554</v>
       </c>
       <c r="P4" t="n">
-        <v>329.1287718262288</v>
+        <v>329.1798897387916</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21957,28 +22061,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09597172287889798</v>
+        <v>0.09206118745451988</v>
       </c>
       <c r="J5" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K5" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06465745933191869</v>
+        <v>0.05979737316584521</v>
       </c>
       <c r="M5" t="n">
-        <v>2.223140907985559</v>
+        <v>2.236172707543574</v>
       </c>
       <c r="N5" t="n">
-        <v>7.478643841992187</v>
+        <v>7.522433715746365</v>
       </c>
       <c r="O5" t="n">
-        <v>2.734710924758262</v>
+        <v>2.742705546672184</v>
       </c>
       <c r="P5" t="n">
-        <v>328.3841653237296</v>
+        <v>328.426491428829</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22039,28 +22143,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1514909152116334</v>
+        <v>-0.1535346578209341</v>
       </c>
       <c r="J6" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K6" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1025308748972357</v>
+        <v>0.1058422445099206</v>
       </c>
       <c r="M6" t="n">
-        <v>2.473033728632265</v>
+        <v>2.473570757551296</v>
       </c>
       <c r="N6" t="n">
-        <v>11.27514794282886</v>
+        <v>11.24174755675194</v>
       </c>
       <c r="O6" t="n">
-        <v>3.357848707555012</v>
+        <v>3.352871538957606</v>
       </c>
       <c r="P6" t="n">
-        <v>328.6764963137477</v>
+        <v>328.6986151673004</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22121,28 +22225,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1489209207844031</v>
+        <v>0.1466146080623948</v>
       </c>
       <c r="J7" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K7" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07801584850770216</v>
+        <v>0.07641140806151825</v>
       </c>
       <c r="M7" t="n">
-        <v>2.90947447524171</v>
+        <v>2.907579683123686</v>
       </c>
       <c r="N7" t="n">
-        <v>14.71079901131587</v>
+        <v>14.66698053868866</v>
       </c>
       <c r="O7" t="n">
-        <v>3.835465944486519</v>
+        <v>3.82974940938551</v>
       </c>
       <c r="P7" t="n">
-        <v>313.3708749400881</v>
+        <v>313.3958329824324</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22199,28 +22303,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02317790589374367</v>
+        <v>0.01760730282131087</v>
       </c>
       <c r="J8" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K8" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002619752411353371</v>
+        <v>0.001508053762757089</v>
       </c>
       <c r="M8" t="n">
-        <v>2.654610302722112</v>
+        <v>2.674107196045664</v>
       </c>
       <c r="N8" t="n">
-        <v>11.47976827018505</v>
+        <v>11.58722072088692</v>
       </c>
       <c r="O8" t="n">
-        <v>3.388180672600718</v>
+        <v>3.404000693432203</v>
       </c>
       <c r="P8" t="n">
-        <v>323.5119636348245</v>
+        <v>323.5722547521216</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22277,28 +22381,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02449539077650419</v>
+        <v>-0.02830073347079319</v>
       </c>
       <c r="J9" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K9" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004264582620378765</v>
+        <v>0.005689207454079859</v>
       </c>
       <c r="M9" t="n">
-        <v>2.209998277733615</v>
+        <v>2.216760378203638</v>
       </c>
       <c r="N9" t="n">
-        <v>7.863581337328823</v>
+        <v>7.901901952179408</v>
       </c>
       <c r="O9" t="n">
-        <v>2.804207791396498</v>
+        <v>2.811032186258174</v>
       </c>
       <c r="P9" t="n">
-        <v>326.3863674431867</v>
+        <v>326.4275503134887</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22355,28 +22459,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1069603718150688</v>
+        <v>0.1032293633265265</v>
       </c>
       <c r="J10" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K10" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08639447884942553</v>
+        <v>0.08094055034723358</v>
       </c>
       <c r="M10" t="n">
-        <v>2.110952998275613</v>
+        <v>2.119141921236322</v>
       </c>
       <c r="N10" t="n">
-        <v>6.790515594490346</v>
+        <v>6.830457923721058</v>
       </c>
       <c r="O10" t="n">
-        <v>2.605861775783656</v>
+        <v>2.613514477427102</v>
       </c>
       <c r="P10" t="n">
-        <v>324.1154012496945</v>
+        <v>324.155784320937</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22433,28 +22537,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08739450530709111</v>
+        <v>-0.0914701609412866</v>
       </c>
       <c r="J11" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K11" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07127370011339118</v>
+        <v>0.07719215465051621</v>
       </c>
       <c r="M11" t="n">
-        <v>1.885837031121971</v>
+        <v>1.896562584961712</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5861283791939</v>
+        <v>5.646285992817908</v>
       </c>
       <c r="O11" t="n">
-        <v>2.363499181128248</v>
+        <v>2.37619148908877</v>
       </c>
       <c r="P11" t="n">
-        <v>330.0589538616254</v>
+        <v>330.1030659506639</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22492,7 +22596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L405"/>
+  <dimension ref="A1:L407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47605,6 +47709,130 @@
         </is>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>-42.74882622337778,173.393725614217</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>-42.749440667367935,173.39339457184383</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>-42.75006841223878,173.39306438112976</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>-42.75070971086873,173.39278205711992</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>-42.751324754828296,173.39254581881704</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>-42.75186964213987,173.39214510575104</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>-42.75246187466008,173.39174798562672</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>-42.75310664821193,173.39145921338374</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>-42.75372483313076,173.39116374010518</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>-42.75432805360582,173.39081625165858</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>-42.7488300453033,173.39373681286747</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>-42.749440288957494,173.3933934630569</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>-42.75006825002041,173.39306368180405</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>-42.75070991799799,173.39278349624226</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>-42.75132553891337,173.39254932683986</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>-42.75187233149775,173.39215284188765</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>-42.752463971364925,173.39175420911647</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>-42.75310897771791,173.39146768548738</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>-42.7537251659898,173.39116487555017</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>-42.754329035756996,173.39081940301625</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0401/nzd0401.xlsx
+++ b/data/nzd0401/nzd0401.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L407"/>
+  <dimension ref="A1:L408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17540,6 +17540,48 @@
         <v>323.59</v>
       </c>
       <c r="L407" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>328.45</v>
+      </c>
+      <c r="C408" t="n">
+        <v>330.94</v>
+      </c>
+      <c r="D408" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="E408" t="n">
+        <v>327.06</v>
+      </c>
+      <c r="F408" t="n">
+        <v>322.66</v>
+      </c>
+      <c r="G408" t="n">
+        <v>315.66</v>
+      </c>
+      <c r="H408" t="n">
+        <v>318.58</v>
+      </c>
+      <c r="I408" t="n">
+        <v>322.57</v>
+      </c>
+      <c r="J408" t="n">
+        <v>323.3</v>
+      </c>
+      <c r="K408" t="n">
+        <v>323.68</v>
+      </c>
+      <c r="L408" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17556,7 +17598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21659,6 +21701,16 @@
       </c>
       <c r="B410" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -21827,28 +21879,28 @@
         <v>0.1636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7474032211086346</v>
+        <v>0.7440366951424368</v>
       </c>
       <c r="J2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L2" t="n">
-        <v>0.528941476139415</v>
+        <v>0.5269486105457315</v>
       </c>
       <c r="M2" t="n">
-        <v>4.426448838015467</v>
+        <v>4.431114088298303</v>
       </c>
       <c r="N2" t="n">
-        <v>28.0829706024877</v>
+        <v>28.13429153017479</v>
       </c>
       <c r="O2" t="n">
-        <v>5.299336807798472</v>
+        <v>5.304176800425754</v>
       </c>
       <c r="P2" t="n">
-        <v>315.2768065638746</v>
+        <v>315.3133649904871</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21905,28 +21957,28 @@
         <v>0.1733</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7364389270698364</v>
+        <v>0.7335992894323748</v>
       </c>
       <c r="J3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4782621518926565</v>
+        <v>0.4770209955434325</v>
       </c>
       <c r="M3" t="n">
-        <v>4.673679261902903</v>
+        <v>4.673949223467997</v>
       </c>
       <c r="N3" t="n">
-        <v>33.39840088082136</v>
+        <v>33.4019466551325</v>
       </c>
       <c r="O3" t="n">
-        <v>5.779134959561107</v>
+        <v>5.779441725212955</v>
       </c>
       <c r="P3" t="n">
-        <v>316.9619883782142</v>
+        <v>316.9928251176949</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21983,28 +22035,28 @@
         <v>0.1687</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4574042218304851</v>
+        <v>0.4549897384943986</v>
       </c>
       <c r="J4" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K4" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3653041132514294</v>
+        <v>0.3633851104025055</v>
       </c>
       <c r="M4" t="n">
-        <v>3.564697109906596</v>
+        <v>3.568527556543038</v>
       </c>
       <c r="N4" t="n">
-        <v>20.51999875693141</v>
+        <v>20.53147177013681</v>
       </c>
       <c r="O4" t="n">
-        <v>4.5299005239554</v>
+        <v>4.531166711801367</v>
       </c>
       <c r="P4" t="n">
-        <v>329.1798897387916</v>
+        <v>329.2061095608681</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22061,28 +22113,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09206118745451988</v>
+        <v>0.09021556369256674</v>
       </c>
       <c r="J5" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K5" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05979737316584521</v>
+        <v>0.05758813109181038</v>
       </c>
       <c r="M5" t="n">
-        <v>2.236172707543574</v>
+        <v>2.242081082131154</v>
       </c>
       <c r="N5" t="n">
-        <v>7.522433715746365</v>
+        <v>7.540113983405132</v>
       </c>
       <c r="O5" t="n">
-        <v>2.742705546672184</v>
+        <v>2.745926798624671</v>
       </c>
       <c r="P5" t="n">
-        <v>328.426491428829</v>
+        <v>328.4465337815489</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22143,28 +22195,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1535346578209341</v>
+        <v>-0.1544382249432246</v>
       </c>
       <c r="J6" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K6" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1058422445099206</v>
+        <v>0.107393029712707</v>
       </c>
       <c r="M6" t="n">
-        <v>2.473570757551296</v>
+        <v>2.473064068599426</v>
       </c>
       <c r="N6" t="n">
-        <v>11.24174755675194</v>
+        <v>11.22279413448988</v>
       </c>
       <c r="O6" t="n">
-        <v>3.352871538957606</v>
+        <v>3.350043900382483</v>
       </c>
       <c r="P6" t="n">
-        <v>328.6986151673004</v>
+        <v>328.7084273572735</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22225,28 +22277,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1466146080623948</v>
+        <v>0.1458028291961698</v>
       </c>
       <c r="J7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07641140806151825</v>
+        <v>0.07597050205926881</v>
       </c>
       <c r="M7" t="n">
-        <v>2.907579683123686</v>
+        <v>2.904817981849863</v>
       </c>
       <c r="N7" t="n">
-        <v>14.66698053868866</v>
+        <v>14.63793977423083</v>
       </c>
       <c r="O7" t="n">
-        <v>3.82974940938551</v>
+        <v>3.825956060154224</v>
       </c>
       <c r="P7" t="n">
-        <v>313.3958329824324</v>
+        <v>313.4046484077118</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22303,28 +22355,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01760730282131087</v>
+        <v>0.01498611756213205</v>
       </c>
       <c r="J8" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K8" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001508053762757089</v>
+        <v>0.001091862980900582</v>
       </c>
       <c r="M8" t="n">
-        <v>2.674107196045664</v>
+        <v>2.683642354160169</v>
       </c>
       <c r="N8" t="n">
-        <v>11.58722072088692</v>
+        <v>11.63169200778378</v>
       </c>
       <c r="O8" t="n">
-        <v>3.404000693432203</v>
+        <v>3.410526646690183</v>
       </c>
       <c r="P8" t="n">
-        <v>323.5722547521216</v>
+        <v>323.6007192314981</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22381,28 +22433,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02830073347079319</v>
+        <v>-0.0297827536299318</v>
       </c>
       <c r="J9" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K9" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005689207454079859</v>
+        <v>0.006311622918927395</v>
       </c>
       <c r="M9" t="n">
-        <v>2.216760378203638</v>
+        <v>2.218305374183692</v>
       </c>
       <c r="N9" t="n">
-        <v>7.901901952179408</v>
+        <v>7.905804632057462</v>
       </c>
       <c r="O9" t="n">
-        <v>2.811032186258174</v>
+        <v>2.811726272605045</v>
       </c>
       <c r="P9" t="n">
-        <v>326.4275503134887</v>
+        <v>326.4436441519947</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22459,28 +22511,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1032293633265265</v>
+        <v>0.1014822264801162</v>
       </c>
       <c r="J10" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K10" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08094055034723358</v>
+        <v>0.07847847973276523</v>
       </c>
       <c r="M10" t="n">
-        <v>2.119141921236322</v>
+        <v>2.122685928021734</v>
       </c>
       <c r="N10" t="n">
-        <v>6.830457923721058</v>
+        <v>6.846081874164001</v>
       </c>
       <c r="O10" t="n">
-        <v>2.613514477427102</v>
+        <v>2.616501839128725</v>
       </c>
       <c r="P10" t="n">
-        <v>324.155784320937</v>
+        <v>324.1747571655914</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22537,28 +22589,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0914701609412866</v>
+        <v>-0.09336502075247077</v>
       </c>
       <c r="J11" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K11" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07719215465051621</v>
+        <v>0.08005928564426978</v>
       </c>
       <c r="M11" t="n">
-        <v>1.896562584961712</v>
+        <v>1.901167054903028</v>
       </c>
       <c r="N11" t="n">
-        <v>5.646285992817908</v>
+        <v>5.670531145339975</v>
       </c>
       <c r="O11" t="n">
-        <v>2.37619148908877</v>
+        <v>2.381287707384384</v>
       </c>
       <c r="P11" t="n">
-        <v>330.1030659506639</v>
+        <v>330.1236429769645</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22596,7 +22648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L407"/>
+  <dimension ref="A1:L408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47833,6 +47885,68 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-42.74883121836933,173.39374025007731</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>-42.74943824554082,173.39338747560765</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-42.750067898547265,173.39306216659838</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-42.75071010786644,173.39278481543775</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-42.7513256695942,173.39254991151034</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-42.7518735993377,173.3921564889237</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-42.75246385904147,173.39175387571524</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>-42.7531103628293,173.39147272295475</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-42.75372563199244,173.39116646517314</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>-42.75432935144842,173.39082041595265</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
